--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/176.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/176.xlsx
@@ -426,13 +426,13 @@
         <v>-5.281547824240525</v>
       </c>
       <c r="E2">
-        <v>-8.096900017000179</v>
+        <v>-8.774568038352017</v>
       </c>
       <c r="F2">
-        <v>3.205148522255614</v>
+        <v>3.150559763056332</v>
       </c>
       <c r="G2">
-        <v>-9.814609983668658</v>
+        <v>-11.92792983411781</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.026411551308198</v>
       </c>
       <c r="E3">
-        <v>-8.571456922159985</v>
+        <v>-7.559859227482535</v>
       </c>
       <c r="F3">
-        <v>3.024414419479749</v>
+        <v>3.509422772377165</v>
       </c>
       <c r="G3">
-        <v>-10.80905151602817</v>
+        <v>-10.68946799005862</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.622465890339385</v>
       </c>
       <c r="E4">
-        <v>-8.12282553069409</v>
+        <v>-9.571257942047454</v>
       </c>
       <c r="F4">
-        <v>2.988298006078153</v>
+        <v>3.807555410958641</v>
       </c>
       <c r="G4">
-        <v>-9.639644341372637</v>
+        <v>-10.33173043908497</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.12317398391231</v>
       </c>
       <c r="E5">
-        <v>-9.901759560549261</v>
+        <v>-9.978245486538812</v>
       </c>
       <c r="F5">
-        <v>3.410881422906691</v>
+        <v>3.819732525742455</v>
       </c>
       <c r="G5">
-        <v>-9.20683685975048</v>
+        <v>-10.15881071393222</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.541471533614905</v>
       </c>
       <c r="E6">
-        <v>-10.23868708366795</v>
+        <v>-10.93020317853524</v>
       </c>
       <c r="F6">
-        <v>3.383385120802831</v>
+        <v>3.654398379288323</v>
       </c>
       <c r="G6">
-        <v>-8.564329492034267</v>
+        <v>-9.621913059464301</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.915832235645374</v>
       </c>
       <c r="E7">
-        <v>-10.24109170336602</v>
+        <v>-11.19882319972223</v>
       </c>
       <c r="F7">
-        <v>3.726623287561938</v>
+        <v>3.735480954746991</v>
       </c>
       <c r="G7">
-        <v>-7.698658249515783</v>
+        <v>-8.546700837037648</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.274958242747941</v>
       </c>
       <c r="E8">
-        <v>-11.58208606888741</v>
+        <v>-13.84214329121351</v>
       </c>
       <c r="F8">
-        <v>3.694651432541047</v>
+        <v>3.588452864969424</v>
       </c>
       <c r="G8">
-        <v>-7.53041963575556</v>
+        <v>-8.171334631067383</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.655029085663678</v>
       </c>
       <c r="E9">
-        <v>-12.03489724186238</v>
+        <v>-12.37742195885455</v>
       </c>
       <c r="F9">
-        <v>4.113606579117314</v>
+        <v>3.638366524306329</v>
       </c>
       <c r="G9">
-        <v>-6.582640242772073</v>
+        <v>-7.345267444835201</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.084959393969492</v>
       </c>
       <c r="E10">
-        <v>-12.41153948202834</v>
+        <v>-12.49288446062812</v>
       </c>
       <c r="F10">
-        <v>4.125835956196337</v>
+        <v>4.220647678235951</v>
       </c>
       <c r="G10">
-        <v>-5.792078657448575</v>
+        <v>-6.943589022918811</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.5868505966917602</v>
       </c>
       <c r="E11">
-        <v>-13.92993681680021</v>
+        <v>-14.28775419051629</v>
       </c>
       <c r="F11">
-        <v>4.070003987853434</v>
+        <v>4.169364113282191</v>
       </c>
       <c r="G11">
-        <v>-5.02216494465351</v>
+        <v>-5.375317390055264</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.1759698527132955</v>
       </c>
       <c r="E12">
-        <v>-13.92158178225606</v>
+        <v>-15.10502600857659</v>
       </c>
       <c r="F12">
-        <v>4.249228818891886</v>
+        <v>4.613701314565205</v>
       </c>
       <c r="G12">
-        <v>-4.686469005880333</v>
+        <v>-6.490189948042386</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.1465553666271262</v>
       </c>
       <c r="E13">
-        <v>-14.98182887319791</v>
+        <v>-15.45003685779897</v>
       </c>
       <c r="F13">
-        <v>4.654228348941301</v>
+        <v>4.604384372664675</v>
       </c>
       <c r="G13">
-        <v>-4.331753982984043</v>
+        <v>-4.763836455133101</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.3827635629808578</v>
       </c>
       <c r="E14">
-        <v>-16.82412983984241</v>
+        <v>-17.55842190018616</v>
       </c>
       <c r="F14">
-        <v>4.904159314280462</v>
+        <v>5.017666684651838</v>
       </c>
       <c r="G14">
-        <v>-4.479659226042062</v>
+        <v>-4.206300859773362</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.5497654886048206</v>
       </c>
       <c r="E15">
-        <v>-16.27516104978857</v>
+        <v>-18.52318158820228</v>
       </c>
       <c r="F15">
-        <v>5.374814540466249</v>
+        <v>5.167998384969012</v>
       </c>
       <c r="G15">
-        <v>-3.380220431359022</v>
+        <v>-2.988685520974959</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.6672559368381231</v>
       </c>
       <c r="E16">
-        <v>-17.1723876049283</v>
+        <v>-18.20226674917471</v>
       </c>
       <c r="F16">
-        <v>5.202493083513199</v>
+        <v>5.382937368106538</v>
       </c>
       <c r="G16">
-        <v>-2.777108555560137</v>
+        <v>-2.248864667131869</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.7605940593751586</v>
       </c>
       <c r="E17">
-        <v>-18.17150935371462</v>
+        <v>-19.52934964254453</v>
       </c>
       <c r="F17">
-        <v>5.579958302516783</v>
+        <v>5.833528624049624</v>
       </c>
       <c r="G17">
-        <v>-2.851681904377759</v>
+        <v>-3.974976490216787</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.8517771068086827</v>
       </c>
       <c r="E18">
-        <v>-19.78061655133413</v>
+        <v>-19.91990788333606</v>
       </c>
       <c r="F18">
-        <v>5.777815433650379</v>
+        <v>5.742416439028476</v>
       </c>
       <c r="G18">
-        <v>-2.098102423273459</v>
+        <v>-3.124513893905716</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.9584800980184232</v>
       </c>
       <c r="E19">
-        <v>-20.99955042845277</v>
+        <v>-20.89394188611989</v>
       </c>
       <c r="F19">
-        <v>5.988620944348608</v>
+        <v>5.730885476258162</v>
       </c>
       <c r="G19">
-        <v>-2.315039161916361</v>
+        <v>-2.338507619244254</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.08852250670734</v>
       </c>
       <c r="E20">
-        <v>-19.79132639236227</v>
+        <v>-21.50071664688165</v>
       </c>
       <c r="F20">
-        <v>6.094198699201379</v>
+        <v>6.144891541848681</v>
       </c>
       <c r="G20">
-        <v>-1.63572845944007</v>
+        <v>-2.245713027778483</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.238164634277874</v>
       </c>
       <c r="E21">
-        <v>-20.98987307949838</v>
+        <v>-20.58849178582851</v>
       </c>
       <c r="F21">
-        <v>6.206705167434198</v>
+        <v>6.488836041446073</v>
       </c>
       <c r="G21">
-        <v>-1.858326230955126</v>
+        <v>-1.256959012655436</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.392229663209328</v>
       </c>
       <c r="E22">
-        <v>-22.63978635640101</v>
+        <v>-22.35696051225196</v>
       </c>
       <c r="F22">
-        <v>6.371546781348628</v>
+        <v>6.659426507833549</v>
       </c>
       <c r="G22">
-        <v>-1.825396234475995</v>
+        <v>-1.846507583379928</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.526026331123868</v>
       </c>
       <c r="E23">
-        <v>-22.50044068271098</v>
+        <v>-23.99852781155845</v>
       </c>
       <c r="F23">
-        <v>6.439638217182947</v>
+        <v>6.41078309540364</v>
       </c>
       <c r="G23">
-        <v>-1.029206721735735</v>
+        <v>-1.656565033064243</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.61277886746726</v>
       </c>
       <c r="E24">
-        <v>-23.24502143600016</v>
+        <v>-23.13138843772569</v>
       </c>
       <c r="F24">
-        <v>6.40343153254417</v>
+        <v>6.225947194306787</v>
       </c>
       <c r="G24">
-        <v>-1.962648141988639</v>
+        <v>-1.415911546178003</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.627085440685048</v>
       </c>
       <c r="E25">
-        <v>-21.87543881406835</v>
+        <v>-24.19811124649851</v>
       </c>
       <c r="F25">
-        <v>6.442225992648775</v>
+        <v>6.438754509282131</v>
       </c>
       <c r="G25">
-        <v>-1.959145584808091</v>
+        <v>-2.711324705149279</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.552375705297146</v>
       </c>
       <c r="E26">
-        <v>-22.58633224921447</v>
+        <v>-24.14421334885922</v>
       </c>
       <c r="F26">
-        <v>6.439155186878738</v>
+        <v>6.357131890106298</v>
       </c>
       <c r="G26">
-        <v>-1.636430295094396</v>
+        <v>-3.296847652498017</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.377758905075319</v>
       </c>
       <c r="E27">
-        <v>-23.07427532354095</v>
+        <v>-23.81318189889851</v>
       </c>
       <c r="F27">
-        <v>6.375159214541745</v>
+        <v>6.405252794346926</v>
       </c>
       <c r="G27">
-        <v>-1.353140292207882</v>
+        <v>-2.26212671256219</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.104033107949028</v>
       </c>
       <c r="E28">
-        <v>-23.81513819966983</v>
+        <v>-24.32886187652198</v>
       </c>
       <c r="F28">
-        <v>6.39952136263895</v>
+        <v>6.414895979666037</v>
       </c>
       <c r="G28">
-        <v>-0.6614282861414814</v>
+        <v>-2.741533433195129</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.7383192018340561</v>
       </c>
       <c r="E29">
-        <v>-22.85089022921658</v>
+        <v>-23.09604822656983</v>
       </c>
       <c r="F29">
-        <v>6.21240650872978</v>
+        <v>6.650635356296944</v>
       </c>
       <c r="G29">
-        <v>-1.875004759381974</v>
+        <v>-2.346254295806149</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.2973735120145014</v>
       </c>
       <c r="E30">
-        <v>-21.86545352888144</v>
+        <v>-23.16337304964186</v>
       </c>
       <c r="F30">
-        <v>6.168255955219159</v>
+        <v>6.511893215868956</v>
       </c>
       <c r="G30">
-        <v>-1.406026257197739</v>
+        <v>-1.712596016316408</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.1959992768374027</v>
       </c>
       <c r="E31">
-        <v>-22.82856485235876</v>
+        <v>-23.2775766356413</v>
       </c>
       <c r="F31">
-        <v>6.379568251810329</v>
+        <v>6.136542244262484</v>
       </c>
       <c r="G31">
-        <v>-1.604258413543759</v>
+        <v>-2.853840380069364</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.7147091254294333</v>
       </c>
       <c r="E32">
-        <v>-21.56018003907636</v>
+        <v>-23.34173605538198</v>
       </c>
       <c r="F32">
-        <v>6.519548850264191</v>
+        <v>6.210685020399697</v>
       </c>
       <c r="G32">
-        <v>-1.709722462788321</v>
+        <v>-3.481579404134888</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.229100478501858</v>
       </c>
       <c r="E33">
-        <v>-20.99753978599336</v>
+        <v>-21.31154417368522</v>
       </c>
       <c r="F33">
-        <v>5.942064741552435</v>
+        <v>6.31547725711841</v>
       </c>
       <c r="G33">
-        <v>-2.826889228834158</v>
+        <v>-2.080351278091887</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.712034994524698</v>
       </c>
       <c r="E34">
-        <v>-22.055296216231</v>
+        <v>-22.91610931187505</v>
       </c>
       <c r="F34">
-        <v>6.28729362664725</v>
+        <v>6.151951702819709</v>
       </c>
       <c r="G34">
-        <v>-2.740351568437609</v>
+        <v>-3.830663189068878</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.138691837069223</v>
       </c>
       <c r="E35">
-        <v>-20.66020017173997</v>
+        <v>-20.99010403167277</v>
       </c>
       <c r="F35">
-        <v>6.389437907075347</v>
+        <v>6.176229914503397</v>
       </c>
       <c r="G35">
-        <v>-1.825459134841241</v>
+        <v>-3.656296755515465</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.492441431360421</v>
       </c>
       <c r="E36">
-        <v>-21.05910439012764</v>
+        <v>-21.88242172098818</v>
       </c>
       <c r="F36">
-        <v>6.069632253041083</v>
+        <v>5.845419088062743</v>
       </c>
       <c r="G36">
-        <v>-2.615252673599629</v>
+        <v>-2.91109295462552</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.76279436341489</v>
       </c>
       <c r="E37">
-        <v>-19.44852090998162</v>
+        <v>-20.33991026212546</v>
       </c>
       <c r="F37">
-        <v>6.007904147574999</v>
+        <v>6.259089407999189</v>
       </c>
       <c r="G37">
-        <v>-2.34456922812666</v>
+        <v>-3.261017618126485</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.951892088864415</v>
       </c>
       <c r="E38">
-        <v>-18.43159772987115</v>
+        <v>-21.22668509925549</v>
       </c>
       <c r="F38">
-        <v>6.226203754665088</v>
+        <v>6.363024859817648</v>
       </c>
       <c r="G38">
-        <v>-2.332121576899</v>
+        <v>-3.497330979810741</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.067220629497384</v>
       </c>
       <c r="E39">
-        <v>-18.30801114572782</v>
+        <v>-20.98949268768173</v>
       </c>
       <c r="F39">
-        <v>6.148174564211387</v>
+        <v>6.10200478565858</v>
       </c>
       <c r="G39">
-        <v>-3.080814692787336</v>
+        <v>-2.611720321509227</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.126807753455328</v>
       </c>
       <c r="E40">
-        <v>-17.54653465591603</v>
+        <v>-18.88352132194062</v>
       </c>
       <c r="F40">
-        <v>6.033341631988788</v>
+        <v>6.175015212066254</v>
       </c>
       <c r="G40">
-        <v>-3.701674403222255</v>
+        <v>-3.127827749990526</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.150008441479026</v>
       </c>
       <c r="E41">
-        <v>-18.18806545468666</v>
+        <v>-19.6419184494272</v>
       </c>
       <c r="F41">
-        <v>6.579257730688089</v>
+        <v>6.275399995222299</v>
       </c>
       <c r="G41">
-        <v>-2.930095486020937</v>
+        <v>-3.590986313116722</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.158739300223074</v>
       </c>
       <c r="E42">
-        <v>-17.41939774815068</v>
+        <v>-18.26214676097814</v>
       </c>
       <c r="F42">
-        <v>6.108976259098345</v>
+        <v>6.248060480004068</v>
       </c>
       <c r="G42">
-        <v>-2.323865076324058</v>
+        <v>-3.311334599777867</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.172853895057861</v>
       </c>
       <c r="E43">
-        <v>-17.29750028481221</v>
+        <v>-18.09381885363902</v>
       </c>
       <c r="F43">
-        <v>6.151210528451284</v>
+        <v>6.393099435151844</v>
       </c>
       <c r="G43">
-        <v>-2.737878590919773</v>
+        <v>-3.840369708590021</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.206603110956968</v>
       </c>
       <c r="E44">
-        <v>-17.29103815240327</v>
+        <v>-16.89051726879486</v>
       </c>
       <c r="F44">
-        <v>6.450814429828204</v>
+        <v>6.423356136666314</v>
       </c>
       <c r="G44">
-        <v>-3.029994508213984</v>
+        <v>-3.907123548843885</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.27237426181369</v>
       </c>
       <c r="E45">
-        <v>-15.43560913961053</v>
+        <v>-16.0977671374861</v>
       </c>
       <c r="F45">
-        <v>6.299529338549934</v>
+        <v>6.26362039062326</v>
       </c>
       <c r="G45">
-        <v>-3.05108930439022</v>
+        <v>-3.481744931411852</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.369955944436958</v>
       </c>
       <c r="E46">
-        <v>-14.83516065703749</v>
+        <v>-14.74385756409484</v>
       </c>
       <c r="F46">
-        <v>6.324464788188529</v>
+        <v>6.247387404990006</v>
       </c>
       <c r="G46">
-        <v>-3.523146613925977</v>
+        <v>-3.011587875015636</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.502268577033095</v>
       </c>
       <c r="E47">
-        <v>-14.75674560112067</v>
+        <v>-16.78643935067657</v>
       </c>
       <c r="F47">
-        <v>6.545819363989501</v>
+        <v>6.172969064023507</v>
       </c>
       <c r="G47">
-        <v>-3.359360683916075</v>
+        <v>-4.452373709707389</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.656643957920085</v>
       </c>
       <c r="E48">
-        <v>-12.90616658399014</v>
+        <v>-15.39460833594508</v>
       </c>
       <c r="F48">
-        <v>6.684949512366771</v>
+        <v>6.050852668295802</v>
       </c>
       <c r="G48">
-        <v>-3.567047758322253</v>
+        <v>-3.581693611787988</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.829909279042018</v>
       </c>
       <c r="E49">
-        <v>-13.15125665423328</v>
+        <v>-14.4407305709694</v>
       </c>
       <c r="F49">
-        <v>6.202125089926747</v>
+        <v>6.541209196069656</v>
       </c>
       <c r="G49">
-        <v>-3.559920153776202</v>
+        <v>-4.335521383807734</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.005870287643125</v>
       </c>
       <c r="E50">
-        <v>-13.02570924084463</v>
+        <v>-13.35156011654055</v>
       </c>
       <c r="F50">
-        <v>6.578138050605873</v>
+        <v>6.219205358224762</v>
       </c>
       <c r="G50">
-        <v>-3.330499347904708</v>
+        <v>-3.964399297218816</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.179766950174097</v>
       </c>
       <c r="E51">
-        <v>-12.77168449138436</v>
+        <v>-14.48777235896108</v>
       </c>
       <c r="F51">
-        <v>6.311557584977697</v>
+        <v>6.649426988683464</v>
       </c>
       <c r="G51">
-        <v>-3.667390393617562</v>
+        <v>-4.921027778428775</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.341141048704299</v>
       </c>
       <c r="E52">
-        <v>-11.27355207779681</v>
+        <v>-14.5410996688754</v>
       </c>
       <c r="F52">
-        <v>6.59362352704704</v>
+        <v>6.219373231051798</v>
       </c>
       <c r="G52">
-        <v>-3.177773950541511</v>
+        <v>-4.472875918232096</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.487869565502255</v>
       </c>
       <c r="E53">
-        <v>-11.03607890083458</v>
+        <v>-12.63635557413914</v>
       </c>
       <c r="F53">
-        <v>6.547311214961844</v>
+        <v>6.104980569073691</v>
       </c>
       <c r="G53">
-        <v>-3.351537864806777</v>
+        <v>-3.42592913361974</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.620108405906592</v>
       </c>
       <c r="E54">
-        <v>-10.06162827844205</v>
+        <v>-12.9507177112776</v>
       </c>
       <c r="F54">
-        <v>6.618514632920002</v>
+        <v>6.423550932493913</v>
       </c>
       <c r="G54">
-        <v>-4.143559400713094</v>
+        <v>-4.579766812604084</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.738691313484512</v>
       </c>
       <c r="E55">
-        <v>-10.97047942635946</v>
+        <v>-11.96119632738755</v>
       </c>
       <c r="F55">
-        <v>6.279885050374824</v>
+        <v>6.054699489964404</v>
       </c>
       <c r="G55">
-        <v>-4.371702336006429</v>
+        <v>-3.461143406520967</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.851199250562954</v>
       </c>
       <c r="E56">
-        <v>-10.10670018024039</v>
+        <v>-12.35453505121979</v>
       </c>
       <c r="F56">
-        <v>6.628770712428388</v>
+        <v>6.421884873870871</v>
       </c>
       <c r="G56">
-        <v>-3.906398539370785</v>
+        <v>-3.988526553109025</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.956839086012776</v>
       </c>
       <c r="E57">
-        <v>-9.173685095018044</v>
+        <v>-11.63941654982452</v>
       </c>
       <c r="F57">
-        <v>6.516992748916671</v>
+        <v>6.352827377428134</v>
       </c>
       <c r="G57">
-        <v>-4.3938200907543</v>
+        <v>-3.528897031527691</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.065808222612378</v>
       </c>
       <c r="E58">
-        <v>-10.13134866426414</v>
+        <v>-10.7604397449357</v>
       </c>
       <c r="F58">
-        <v>6.365044084859834</v>
+        <v>6.182175146509956</v>
       </c>
       <c r="G58">
-        <v>-3.790688351682178</v>
+        <v>-4.902210637583558</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.173146103486221</v>
       </c>
       <c r="E59">
-        <v>-9.74256105680961</v>
+        <v>-10.53706823603335</v>
       </c>
       <c r="F59">
-        <v>6.506879202940675</v>
+        <v>6.388863021828043</v>
       </c>
       <c r="G59">
-        <v>-4.551325915876204</v>
+        <v>-4.057945382522002</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.287118898578317</v>
       </c>
       <c r="E60">
-        <v>-9.001571383408516</v>
+        <v>-9.09752974763105</v>
       </c>
       <c r="F60">
-        <v>6.167171116667083</v>
+        <v>6.182449127633327</v>
       </c>
       <c r="G60">
-        <v>-4.565485119147668</v>
+        <v>-3.592863392437489</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.399323255601827</v>
       </c>
       <c r="E61">
-        <v>-7.759999664725534</v>
+        <v>-9.920874249335636</v>
       </c>
       <c r="F61">
-        <v>6.17022450167205</v>
+        <v>6.281769660414197</v>
       </c>
       <c r="G61">
-        <v>-4.806244543491164</v>
+        <v>-5.147422745677375</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.512344548127603</v>
       </c>
       <c r="E62">
-        <v>-7.865490466734215</v>
+        <v>-9.650157544683095</v>
       </c>
       <c r="F62">
-        <v>6.428384402947835</v>
+        <v>6.433038914633311</v>
       </c>
       <c r="G62">
-        <v>-4.743546121522908</v>
+        <v>-4.035407188490644</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.617113770906779</v>
       </c>
       <c r="E63">
-        <v>-7.387759101295031</v>
+        <v>-10.14918632338035</v>
       </c>
       <c r="F63">
-        <v>6.409617487849877</v>
+        <v>6.337012490156555</v>
       </c>
       <c r="G63">
-        <v>-4.386176041104123</v>
+        <v>-4.84996029733724</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.710221412493404</v>
       </c>
       <c r="E64">
-        <v>-7.544367317902295</v>
+        <v>-8.337262360379306</v>
       </c>
       <c r="F64">
-        <v>6.230448086518466</v>
+        <v>6.037886867966098</v>
       </c>
       <c r="G64">
-        <v>-5.180236873062631</v>
+        <v>-4.538189671176377</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.785900431163284</v>
       </c>
       <c r="E65">
-        <v>-7.144063801046258</v>
+        <v>-7.588533524899104</v>
       </c>
       <c r="F65">
-        <v>6.241290137215564</v>
+        <v>6.188687345234243</v>
       </c>
       <c r="G65">
-        <v>-5.020105785328083</v>
+        <v>-5.827213477256859</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.838278773938716</v>
       </c>
       <c r="E66">
-        <v>-8.134246342141436</v>
+        <v>-8.977212721721257</v>
       </c>
       <c r="F66">
-        <v>6.421872204223547</v>
+        <v>5.987414160441044</v>
       </c>
       <c r="G66">
-        <v>-5.081632274175439</v>
+        <v>-5.43279839225363</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.867883141186659</v>
       </c>
       <c r="E67">
-        <v>-7.221699959433759</v>
+        <v>-8.52607708412912</v>
       </c>
       <c r="F67">
-        <v>6.127770097196865</v>
+        <v>5.82430987191585</v>
       </c>
       <c r="G67">
-        <v>-5.13626951775557</v>
+        <v>-5.670671020886882</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.868665521505229</v>
       </c>
       <c r="E68">
-        <v>-6.151770991063507</v>
+        <v>-8.758600639000971</v>
       </c>
       <c r="F68">
-        <v>5.934434446451847</v>
+        <v>6.032540276795575</v>
       </c>
       <c r="G68">
-        <v>-5.36765678767739</v>
+        <v>-5.481943440784111</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.848783594697423</v>
       </c>
       <c r="E69">
-        <v>-7.159510425886422</v>
+        <v>-7.843328114940676</v>
       </c>
       <c r="F69">
-        <v>5.486307436913187</v>
+        <v>5.457621771666831</v>
       </c>
       <c r="G69">
-        <v>-5.311592698969833</v>
+        <v>-5.555202503022643</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.803380991124704</v>
       </c>
       <c r="E70">
-        <v>-7.060486284760694</v>
+        <v>-8.377443510249364</v>
       </c>
       <c r="F70">
-        <v>5.390154315963196</v>
+        <v>5.811041583756299</v>
       </c>
       <c r="G70">
-        <v>-5.682522773917473</v>
+        <v>-5.711033192101676</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.743922992953084</v>
       </c>
       <c r="E71">
-        <v>-7.189199101480709</v>
+        <v>-7.854223623403131</v>
       </c>
       <c r="F71">
-        <v>5.968256069981972</v>
+        <v>5.357124545390791</v>
       </c>
       <c r="G71">
-        <v>-5.53109511040567</v>
+        <v>-5.662530389405815</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.666134351667846</v>
       </c>
       <c r="E72">
-        <v>-6.221106456594947</v>
+        <v>-8.215817744441601</v>
       </c>
       <c r="F72">
-        <v>5.508461898964269</v>
+        <v>5.239266734869703</v>
       </c>
       <c r="G72">
-        <v>-4.950862414828687</v>
+        <v>-5.566941697504898</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.579195853759834</v>
       </c>
       <c r="E73">
-        <v>-7.224299303514162</v>
+        <v>-7.932779062014189</v>
       </c>
       <c r="F73">
-        <v>5.487989332595383</v>
+        <v>5.729764212470031</v>
       </c>
       <c r="G73">
-        <v>-5.235711684664198</v>
+        <v>-5.701786838410492</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.480543920803569</v>
       </c>
       <c r="E74">
-        <v>-7.391603775727543</v>
+        <v>-7.802037488938738</v>
       </c>
       <c r="F74">
-        <v>5.217161367701999</v>
+        <v>5.097927316740393</v>
       </c>
       <c r="G74">
-        <v>-5.158268092864027</v>
+        <v>-6.178230620785784</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.373795769648415</v>
       </c>
       <c r="E75">
-        <v>-6.917259708846096</v>
+        <v>-7.678491661061475</v>
       </c>
       <c r="F75">
-        <v>5.250675752284528</v>
+        <v>5.052584232675446</v>
       </c>
       <c r="G75">
-        <v>-5.385626428864555</v>
+        <v>-5.240578186606927</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.257560284382757</v>
       </c>
       <c r="E76">
-        <v>-6.675199187714092</v>
+        <v>-9.048015412831184</v>
       </c>
       <c r="F76">
-        <v>5.001474875372385</v>
+        <v>4.784711463020273</v>
       </c>
       <c r="G76">
-        <v>-4.280725234041717</v>
+        <v>-5.553219486244619</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.129568396920763</v>
       </c>
       <c r="E77">
-        <v>-8.811207921548077</v>
+        <v>-9.994905742413032</v>
       </c>
       <c r="F77">
-        <v>5.360860507645312</v>
+        <v>5.278186307741627</v>
       </c>
       <c r="G77">
-        <v>-4.8511454726403</v>
+        <v>-5.70756705092206</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.991117648295141</v>
       </c>
       <c r="E78">
-        <v>-7.875380653966968</v>
+        <v>-10.46617950391728</v>
       </c>
       <c r="F78">
-        <v>5.16036967357434</v>
+        <v>5.064686913281235</v>
       </c>
       <c r="G78">
-        <v>-5.052823906892701</v>
+        <v>-4.817497087779148</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.836484259305553</v>
       </c>
       <c r="E79">
-        <v>-8.128789530962193</v>
+        <v>-11.00772612507255</v>
       </c>
       <c r="F79">
-        <v>5.087143863162166</v>
+        <v>4.854332758768906</v>
       </c>
       <c r="G79">
-        <v>-5.510304884419047</v>
+        <v>-5.200255741938603</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.67264776625341</v>
       </c>
       <c r="E80">
-        <v>-9.310431424627666</v>
+        <v>-11.3083217012277</v>
       </c>
       <c r="F80">
-        <v>5.154464034215667</v>
+        <v>5.282817063838372</v>
       </c>
       <c r="G80">
-        <v>-4.643097548770341</v>
+        <v>-5.110652516372689</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.495076265866766</v>
       </c>
       <c r="E81">
-        <v>-10.83558524261898</v>
+        <v>-11.05232253710009</v>
       </c>
       <c r="F81">
-        <v>5.063345514370858</v>
+        <v>4.996085524142145</v>
       </c>
       <c r="G81">
-        <v>-4.492576974736298</v>
+        <v>-4.901439280472908</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.318516951541718</v>
       </c>
       <c r="E82">
-        <v>-9.505735451630473</v>
+        <v>-10.517967132669</v>
       </c>
       <c r="F82">
-        <v>4.859332518343948</v>
+        <v>4.652231295781932</v>
       </c>
       <c r="G82">
-        <v>-4.823525591206161</v>
+        <v>-4.191641764125469</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.143840723766964</v>
       </c>
       <c r="E83">
-        <v>-10.93717702850706</v>
+        <v>-12.01710486748625</v>
       </c>
       <c r="F83">
-        <v>5.079695694241854</v>
+        <v>4.363993651760121</v>
       </c>
       <c r="G83">
-        <v>-3.213643711459514</v>
+        <v>-3.672621055569611</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.990237018017767</v>
       </c>
       <c r="E84">
-        <v>-12.86084108764737</v>
+        <v>-12.37123153488607</v>
       </c>
       <c r="F84">
-        <v>4.90975771469154</v>
+        <v>4.746914737642395</v>
       </c>
       <c r="G84">
-        <v>-3.379333205154498</v>
+        <v>-4.277845059422551</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.866201853903366</v>
       </c>
       <c r="E85">
-        <v>-13.8844709377632</v>
+        <v>-14.5549115145988</v>
       </c>
       <c r="F85">
-        <v>4.65764915371865</v>
+        <v>5.06099371108643</v>
       </c>
       <c r="G85">
-        <v>-3.395081470284811</v>
+        <v>-4.842859177155504</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.791164821404806</v>
       </c>
       <c r="E86">
-        <v>-14.0101632623201</v>
+        <v>-15.23671403271964</v>
       </c>
       <c r="F86">
-        <v>4.908390976486515</v>
+        <v>4.314241530426591</v>
       </c>
       <c r="G86">
-        <v>-2.849596260688019</v>
+        <v>-3.709864692886411</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.779093522223486</v>
       </c>
       <c r="E87">
-        <v>-16.58847710943126</v>
+        <v>-18.32655524678923</v>
       </c>
       <c r="F87">
-        <v>4.442280986278039</v>
+        <v>4.303361470787522</v>
       </c>
       <c r="G87">
-        <v>-2.335461917348125</v>
+        <v>-3.310993613587323</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.842461394303749</v>
       </c>
       <c r="E88">
-        <v>-17.19444127334565</v>
+        <v>-19.26237345742233</v>
       </c>
       <c r="F88">
-        <v>4.555642655705195</v>
+        <v>3.853118630145834</v>
       </c>
       <c r="G88">
-        <v>-2.912331098657208</v>
+        <v>-2.897887188469368</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.995129002342673</v>
       </c>
       <c r="E89">
-        <v>-18.85148689681036</v>
+        <v>-19.22756760619937</v>
       </c>
       <c r="F89">
-        <v>4.528159023248659</v>
+        <v>3.933621569239451</v>
       </c>
       <c r="G89">
-        <v>-2.414186690271994</v>
+        <v>-3.604648934557295</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.237474570074079</v>
       </c>
       <c r="E90">
-        <v>-19.30395390576076</v>
+        <v>-21.24738022547054</v>
       </c>
       <c r="F90">
-        <v>4.182675161501459</v>
+        <v>3.860091687291513</v>
       </c>
       <c r="G90">
-        <v>-2.745820589668485</v>
+        <v>-2.781756561497274</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.580072091157223</v>
       </c>
       <c r="E91">
-        <v>-21.84369873974859</v>
+        <v>-22.15044851208017</v>
       </c>
       <c r="F91">
-        <v>3.971468973206624</v>
+        <v>3.416405389139744</v>
       </c>
       <c r="G91">
-        <v>-2.408681253040186</v>
+        <v>-2.253340524700964</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.008997125301819</v>
       </c>
       <c r="E92">
-        <v>-24.58454404746905</v>
+        <v>-25.80946909569984</v>
       </c>
       <c r="F92">
-        <v>3.780665668220394</v>
+        <v>3.315995266689052</v>
       </c>
       <c r="G92">
-        <v>-2.255859849856349</v>
+        <v>-1.887031971326146</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.528555468811782</v>
       </c>
       <c r="E93">
-        <v>-26.03889517435044</v>
+        <v>-26.8840080506099</v>
       </c>
       <c r="F93">
-        <v>3.511122088824431</v>
+        <v>3.284783590507572</v>
       </c>
       <c r="G93">
-        <v>-1.840015603577417</v>
+        <v>-1.978820156947979</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.11264893184422</v>
       </c>
       <c r="E94">
-        <v>-28.18482126626122</v>
+        <v>-29.8110823234218</v>
       </c>
       <c r="F94">
-        <v>3.047444670902069</v>
+        <v>2.71864673467994</v>
       </c>
       <c r="G94">
-        <v>-1.989519840130904</v>
+        <v>-1.495321602028501</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.753592664065819</v>
       </c>
       <c r="E95">
-        <v>-29.41332833743208</v>
+        <v>-31.4845323439793</v>
       </c>
       <c r="F95">
-        <v>3.159705664717995</v>
+        <v>2.625689532267306</v>
       </c>
       <c r="G95">
-        <v>-2.135898921695318</v>
+        <v>-2.808466042908114</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.424971894976161</v>
       </c>
       <c r="E96">
-        <v>-32.16907911734879</v>
+        <v>-32.73816565318171</v>
       </c>
       <c r="F96">
-        <v>3.121075910028596</v>
+        <v>2.931591832069928</v>
       </c>
       <c r="G96">
-        <v>-2.355093452396003</v>
+        <v>-1.820092740522083</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.104338730916837</v>
       </c>
       <c r="E97">
-        <v>-34.47776988628026</v>
+        <v>-35.63095711351853</v>
       </c>
       <c r="F97">
-        <v>2.573762982711877</v>
+        <v>2.570212314049462</v>
       </c>
       <c r="G97">
-        <v>-2.75724197177897</v>
+        <v>-2.734541561016188</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.780134273837284</v>
       </c>
       <c r="E98">
-        <v>-37.2353728120661</v>
+        <v>-36.55181551026729</v>
       </c>
       <c r="F98">
-        <v>2.822392141788547</v>
+        <v>2.484765045087842</v>
       </c>
       <c r="G98">
-        <v>-1.671697536724252</v>
+        <v>-2.137739585015153</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.420911216517498</v>
       </c>
       <c r="E99">
-        <v>-39.05838700791194</v>
+        <v>-40.33142482823722</v>
       </c>
       <c r="F99">
-        <v>2.269898912422426</v>
+        <v>1.80106969915714</v>
       </c>
       <c r="G99">
-        <v>-2.001954249176406</v>
+        <v>-2.169282462913329</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.04787567175187</v>
       </c>
       <c r="E100">
-        <v>-41.69902397855366</v>
+        <v>-42.69129414616638</v>
       </c>
       <c r="F100">
-        <v>2.019844418021861</v>
+        <v>2.230482055893054</v>
       </c>
       <c r="G100">
-        <v>-1.683370520295722</v>
+        <v>-1.959337596449368</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.61182007825363</v>
       </c>
       <c r="E101">
-        <v>-44.74297816550353</v>
+        <v>-44.29504415903482</v>
       </c>
       <c r="F101">
-        <v>2.150759883815747</v>
+        <v>1.559362918636856</v>
       </c>
       <c r="G101">
-        <v>-2.110904302873821</v>
+        <v>-3.016553693324543</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.19660493396643</v>
       </c>
       <c r="E102">
-        <v>-46.11858365786554</v>
+        <v>-46.9246746736009</v>
       </c>
       <c r="F102">
-        <v>1.507632748614942</v>
+        <v>0.7987976549825541</v>
       </c>
       <c r="G102">
-        <v>-2.490729813685483</v>
+        <v>-2.986344965278694</v>
       </c>
     </row>
   </sheetData>
